--- a/Kumpulan Link Modul robotic iot IDN (1).xlsx
+++ b/Kumpulan Link Modul robotic iot IDN (1).xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="194">
   <si>
     <t>Materi</t>
   </si>
@@ -98,7 +98,13 @@
     </r>
   </si>
   <si>
+    <t>https://canva.link/5qgqy3ds7ophpl5</t>
+  </si>
+  <si>
     <t>Pemrograman Smart trashbin</t>
+  </si>
+  <si>
+    <t>https://canva.link/d3fipufedbmgp85</t>
   </si>
   <si>
     <t>K3 dalam bekerja</t>
@@ -123,6 +129,9 @@
   </si>
   <si>
     <t>Chatgpt / Google Lens Sebagai pembantu pengenalan awal komponen</t>
+  </si>
+  <si>
+    <t>https://canva.link/qjbfa25g12kg3wn</t>
   </si>
   <si>
     <t>Tinybit Bluetooth Controller</t>
@@ -144,6 +153,9 @@
     </r>
   </si>
   <si>
+    <t>https://canva.link/qbtjved7t7fae34</t>
+  </si>
+  <si>
     <t>1. video demonstrasi dan tutorial
 2. Flyer project tinybit bluetooth controller (pemanfaatan chatgpt untuk pengembangan ide di dunia industri) 
 3. Website personal portofolio
@@ -176,7 +188,13 @@
     </r>
   </si>
   <si>
+    <t>https://canva.link/7fly21p5sidqe5r</t>
+  </si>
+  <si>
     <t>Pemrograman basic untuk menggerakkan tinybit</t>
+  </si>
+  <si>
+    <t>https://canva.link/rnojs4b9gn7132a</t>
   </si>
   <si>
     <t>Integrasi</t>
@@ -249,7 +267,16 @@
     </r>
   </si>
   <si>
+    <t>https://canva.link/7l59t6qrbrpbqo4</t>
+  </si>
+  <si>
     <t>Faktor yang mempengaruhi kualitas model AI pada teachable machine</t>
+  </si>
+  <si>
+    <t>https://canva.link/364c17kqf2sz7d4</t>
+  </si>
+  <si>
+    <t>Integrasi tinybit Hand Gesture</t>
   </si>
   <si>
     <r>
@@ -273,13 +300,16 @@
     </r>
   </si>
   <si>
+    <t>https://docs.google.com/presentation/d/1R06DaJtlH_sF1lY-kkjfk2QNPAVU_KR6/edit?slide=id.p1#slide=id.p1</t>
+  </si>
+  <si>
     <t>Smart Watering Plant</t>
   </si>
   <si>
     <t>Algoritma, konsep, dan komponen smart watering plant</t>
   </si>
   <si>
-    <t>smart watering plant</t>
+    <t>https://docs.google.com/presentation/d/1IZLBFij0V2aRK15UeLotVumJg1eci6Uo/edit?usp=sharing&amp;ouid=112099463869605700691&amp;rtpof=true&amp;sd=true</t>
   </si>
   <si>
     <t>1. video demonstrasi dan tutorial
@@ -294,16 +324,28 @@
     <t>Pemrograman Smart watering plant</t>
   </si>
   <si>
+    <t>https://docs.google.com/presentation/d/1LEB59CeHilt6IkwNsXnAz_4BvICL7Qe5/edit?usp=drive_link&amp;ouid=112099463869605700691&amp;rtpof=true&amp;sd=true</t>
+  </si>
+  <si>
     <t>https://drive.google.com/file/d/18GPMXi9-nlijGMKDGzuXay0cJu6ZIdCD/view?usp=drive_link</t>
   </si>
   <si>
     <t>Integrasi hardware dan program smart watering plant</t>
   </si>
   <si>
+    <t>ChatGPT / Claude: brainstorming ide pengembangan fitur monitoring</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/18ljOfjQpPwaGOj94h3F_uX3ukSTFMLOr/edit?usp=drive_link&amp;ouid=112099463869605700691&amp;rtpof=true&amp;sd=true</t>
+  </si>
+  <si>
     <t>Tinybit Line Follower</t>
   </si>
   <si>
     <t>Fundamental Line Follower</t>
+  </si>
+  <si>
+    <t>fundamental line follower</t>
   </si>
   <si>
     <t xml:space="preserve">1. video demonstrasi dan tutorial
@@ -324,6 +366,9 @@
     <t>Pemrograman basic dan lanjutan untuk menggerakkan line follower</t>
   </si>
   <si>
+    <t>Pemrograman line follower</t>
+  </si>
+  <si>
     <t>Praktek dengan track sederhana</t>
   </si>
   <si>
@@ -334,6 +379,9 @@
   </si>
   <si>
     <t>track advance dengan ai</t>
+  </si>
+  <si>
+    <t>Track advance line follower</t>
   </si>
   <si>
     <t>Smart Parking</t>
@@ -360,10 +408,16 @@
     <t>Pemrograman Smart parking</t>
   </si>
   <si>
+    <t>https://canva.link/85b8zcozo27u4ft</t>
+  </si>
+  <si>
     <t>https://drive.google.com/file/d/1hRZ1vqyA_ixJOPkkFh7Ab0oSh8rxUeX4/view?usp=sharing</t>
   </si>
   <si>
     <t>Integrasi hardware dan program smart parking</t>
+  </si>
+  <si>
+    <t>https://canva.link/wn3pd9uh5musbho</t>
   </si>
   <si>
     <r>
@@ -391,8 +445,11 @@
     </r>
   </si>
   <si>
+    <t>https://docs.google.com/presentation/d/17CRQvkqcS5YY2Lk1W_EVlmpTEbkET9JnpdNOatx3pKQ/edit?usp=sharing</t>
+  </si>
+  <si>
     <t>1. video demonstrasi dan tutorial
-2. Flyer project tinybit bluetooth controller (pemanfaatan chatgpt untuk pengembangan ide di dunia industri) 
+2. Flyer project robot bluetooth controller (pemanfaatan chatgpt untuk pengembangan ide di dunia industri) 
 3. Website personal portofolio
 4. kumpulan deskripsi komponen (pdf), dan fix problem yang dialami
 5. Website interface controller robot (lovable dan vercel)</t>
@@ -407,26 +464,38 @@
     <t>Fundamental driver l298N</t>
   </si>
   <si>
+    <t>https://docs.google.com/presentation/d/15Vdbf_ehjL3n6GhVnsiZn9iSMiIZkOnbfmRKGIZojX0/edit?usp=sharing</t>
+  </si>
+  <si>
     <t>Pemrograman python untuk menggerakkan motor</t>
   </si>
   <si>
+    <t>https://docs.google.com/presentation/d/1_uzwmtAwEvjc2jt8b1iaAmFAFVRCNdLo2F3EtOKb15E/edit?usp=sharing</t>
+  </si>
+  <si>
     <t>Teknik prompting lovable (chatgpt) untuk pembuatan app controller</t>
   </si>
   <si>
+    <t>https://docs.google.com/presentation/d/14Bhzum4DBnZHz18ajL2bfeX5-bHvEnE6POe1nyWF3X8/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/1ZNYB5FgyAvQO3Fle6-EWr96qrxjV9Q83oZ1Fi4m3Scw/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/1W3atKC3J8z4SorKL120tXboWuhJY640XGllqSQZ032o/edit?usp=sharing</t>
+  </si>
+  <si>
     <t>Robot Hand Gesture</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>Teachable Machine</t>
-    </r>
+    <t>Robot Hand Gesture.pdf</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/1oaC3_iL1vlkVhY-mtLmJm3nOH_xcEvEy/edit?usp=drive_link&amp;ouid=113658299168731582914&amp;rtpof=true&amp;sd=true</t>
   </si>
   <si>
     <t>1. video demonstrasi dan tutorial
-2. Flyer project tinybit hand gestures (pemanfaatan chatgpt untuk pengembangan ide di dunia industri) 
+2. Flyer project robot hand gestures (pemanfaatan chatgpt untuk pengembangan ide di dunia industri) 
 3. Website personal portofolio
 4. kumpulan deskripsi komponen (pdf), dan fix problem yang dialami
 5. Website interface AI controller robot (lovable dan vercel)</t>
@@ -435,36 +504,66 @@
     <t>project robot hand gestures</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1XUkzLStxltnQVqLP2xDGG25oC86jpukC/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>rahasia permodelan ai</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>Apa Itu Machine Learning?</t>
-    </r>
+    <t>https://drive.google.com/file/d/1SJhXVP8tRxdIBlGibcH-2F-6w-sGr4w7/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/1qEphLthnE9aUvmieQ1yXBntbBekeL05R/edit?usp=drive_link&amp;ouid=113658299168731582914&amp;rtpof=true&amp;sd=true</t>
   </si>
   <si>
     <t>Pemrograman python untuk robot hand gestures</t>
   </si>
   <si>
+    <t>https://makecode.microbit.org/S62132-14584-63645-60319</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/1902dOdmDZos7HZK3GFGKSnoVN_lsHVfN/edit?usp=drive_link&amp;ouid=113658299168731582914&amp;rtpof=true&amp;sd=true</t>
+  </si>
+  <si>
     <t>Teknik prompting lovable (chatgpt) untuk pembuatan app AI</t>
   </si>
   <si>
+    <t>https://docs.google.com/presentation/d/1S4Y2VZpv5CeRhebC5FWNjf4u_7CrzEZO/edit?usp=drive_link&amp;ouid=113658299168731582914&amp;rtpof=true&amp;sd=true</t>
+  </si>
+  <si>
     <t>Smart Parking AI</t>
   </si>
   <si>
+    <t>1. video demonstrasi dan tutorial
+2. Flyer project Smart Parking AI (pemanfaatan chatgpt untuk pengembangan ide di dunia industri) 
+3. Website personal portofolio
+4. Website interface AI controller robot (lovable dan vercel)</t>
+  </si>
+  <si>
+    <t>project Smart Parking AI</t>
+  </si>
+  <si>
     <t>Pemrograman python untuk smart parking</t>
   </si>
   <si>
-    <t>database</t>
+    <t>https://makecode.microbit.org/S82659-39430-34315-71540</t>
+  </si>
+  <si>
+    <t>Database</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/1p53W65C62q_c3POPJxLl5saD27HMaG3c/edit?usp=drive_link&amp;ouid=113658299168731582914&amp;rtpof=true&amp;sd=true</t>
   </si>
   <si>
     <t>Teknik prompting lovable (chatgpt) untuk pembuatan app control dan monitor</t>
   </si>
   <si>
+    <t>https://docs.google.com/presentation/d/11IlEOH6ISFiEQEOaQK1LcwWB56vOdPJy/edit?usp=drive_link&amp;ouid=113658299168731582914&amp;rtpof=true&amp;sd=true</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/1YAIlIHVF56Glr1DEz3LfOyUtJU3csruJ/edit?usp=drive_link&amp;ouid=113658299168731582914&amp;rtpof=true&amp;sd=true</t>
+  </si>
+  <si>
     <t>K3 dalam projek smart parking</t>
   </si>
   <si>
@@ -474,10 +573,16 @@
     <t>Integrasi hardware dan program smart parking AI</t>
   </si>
   <si>
+    <t>https://docs.google.com/presentation/d/15VPEcRH8diHF0s5alSJUCNrXILxCIgkV/edit?usp=drive_link&amp;ouid=113658299168731582914&amp;rtpof=true&amp;sd=true</t>
+  </si>
+  <si>
     <t>ChatGPT / Claude: brainstorming ide pengembangan smart parking</t>
   </si>
   <si>
     <t>Robot Line Follower</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/1SKlrYPtTg5844ptWnNcLqYPHp2rMT3M5SLFDa-fV3Mo/edit?usp=sharing</t>
   </si>
   <si>
     <t xml:space="preserve">1. video demonstrasi dan tutorial
@@ -492,13 +597,31 @@
     <t>Ms. Nadia</t>
   </si>
   <si>
+    <t>https://docs.google.com/presentation/d/1ETGLF5zAujqcaxBEK_vA7os2sABlJw8VOmqXiluKOr0/edit?usp=sharing</t>
+  </si>
+  <si>
     <t>Pemrograman python basic dan lanjutan untuk menggerakkan line follower</t>
   </si>
   <si>
+    <t>https://docs.google.com/presentation/d/1H0Gu6aJZjRrLf_JjLEhclqgVQf02cgC007Q5IIHnseA/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/1pEvJKqN9yzXjXRQovj3sm7zCfHUZXv_LHzsk-QwR-E8/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/1RFv5K4sBEk0gfAQDoKi-bcr1LEh8h4SY_RmfFritbyk/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/1sKbtq9lkWCKKnSErwqWryT6qz6T-d1zOcc3WrLkIsZk/edit?usp=sharing</t>
+  </si>
+  <si>
     <t>Robot Transporter</t>
   </si>
   <si>
     <t>Algoritma, konsep, dan komponen robot transporter</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/131Kjv4T6P7gteRJ99w_cISCm6G7bbfGz8aB7O21903Q/edit?usp=sharing</t>
   </si>
   <si>
     <t>1. video demonstrasi dan tutorial
@@ -514,10 +637,22 @@
     <t>Pemrograman python untuk robot transporter</t>
   </si>
   <si>
+    <t>https://docs.google.com/presentation/d/1QBll2G4V7Dxg91M14QL-biUxmcYA1Gmq_VWecj2aWZ8/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/1VOnlUoV3BUoca-zuazToy2PJon0dviTl03dpXRUUEzc/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/1GnXOJ8uIDFaqANCKRsm0T4jo2LmV-WcCzsdz8_qmVRM/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/16zxsLnLDufAHGypJq406HjGbiFCAT9ZkY6P6ij_V10o/edit?usp=sharing</t>
+  </si>
+  <si>
     <t>Smart home</t>
   </si>
   <si>
-    <t>Algoritma, konsep, dan komponen smart parking</t>
+    <t>Algoritma, konsep, dan komponen smart home</t>
   </si>
   <si>
     <t>https://www.dicoding.com/blog/algoritma-pemrograman-pengertian-fungsi-dan-jenis/</t>
@@ -551,6 +686,9 @@
     <t>Arduino_Code_Anatomy</t>
   </si>
   <si>
+    <t>database</t>
+  </si>
+  <si>
     <t>https://www.youtube.com/watch?v=aO92B-K4TnQ</t>
   </si>
   <si>
@@ -567,6 +705,9 @@
   </si>
   <si>
     <t>Smart greenhouse</t>
+  </si>
+  <si>
+    <t>Algoritma, konsep, dan komponen smart greenhouse</t>
   </si>
   <si>
     <t>1. video demonstrasi dan tutorial
@@ -592,7 +733,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="12">
+  <fonts count="15">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -633,8 +774,22 @@
       <color rgb="FF0000FF"/>
     </font>
     <font>
+      <u/>
+      <color rgb="FF0000FF"/>
+    </font>
+    <font>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
     </font>
     <font>
       <u/>
@@ -736,7 +891,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -774,95 +929,98 @@
     <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="top"/>
+    </xf>
     <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="top"/>
+    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="3" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf borderId="2" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -1167,13 +1325,15 @@
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="11"/>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="14"/>
+      <c r="D4" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
       <c r="G4" s="11"/>
@@ -1181,11 +1341,13 @@
     </row>
     <row r="5">
       <c r="A5" s="11"/>
-      <c r="B5" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="15"/>
-      <c r="D5" s="16"/>
+      <c r="B5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="13"/>
+      <c r="D5" s="6" t="s">
+        <v>22</v>
+      </c>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="11"/>
@@ -1194,13 +1356,13 @@
     <row r="6">
       <c r="A6" s="11"/>
       <c r="B6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>24</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
@@ -1210,269 +1372,283 @@
     <row r="7">
       <c r="A7" s="11"/>
       <c r="B7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="15"/>
+        <v>26</v>
+      </c>
+      <c r="C7" s="13"/>
       <c r="D7" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
+        <v>27</v>
+      </c>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
       <c r="H7" s="11"/>
     </row>
     <row r="8">
-      <c r="A8" s="18"/>
-      <c r="B8" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="15"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="18"/>
+      <c r="A8" s="15"/>
+      <c r="B8" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="13"/>
+      <c r="D8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="17"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="15"/>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="24" t="s">
-        <v>28</v>
+      <c r="A9" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>31</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="14"/>
+        <v>32</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>33</v>
+      </c>
       <c r="E9" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="25" t="s">
-        <v>31</v>
+        <v>34</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>35</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11"/>
-      <c r="B10" s="24" t="s">
-        <v>34</v>
+      <c r="B10" s="21" t="s">
+        <v>38</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="14"/>
+        <v>39</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>40</v>
+      </c>
       <c r="E10" s="11"/>
-      <c r="F10" s="26"/>
+      <c r="F10" s="23"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
     </row>
     <row r="11">
       <c r="A11" s="11"/>
-      <c r="B11" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="27"/>
-      <c r="D11" s="14"/>
+      <c r="B11" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="24"/>
+      <c r="D11" s="25" t="s">
+        <v>42</v>
+      </c>
       <c r="E11" s="11"/>
-      <c r="F11" s="26"/>
+      <c r="F11" s="23"/>
       <c r="G11" s="11"/>
       <c r="H11" s="11"/>
     </row>
     <row r="12">
       <c r="A12" s="11"/>
-      <c r="B12" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12" s="27"/>
-      <c r="D12" s="14"/>
+      <c r="B12" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="24"/>
+      <c r="D12" s="27"/>
       <c r="E12" s="11"/>
-      <c r="F12" s="26"/>
+      <c r="F12" s="23"/>
       <c r="G12" s="11"/>
       <c r="H12" s="11"/>
     </row>
     <row r="13">
       <c r="A13" s="11"/>
-      <c r="B13" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" s="27"/>
-      <c r="D13" s="14"/>
+      <c r="B13" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="24"/>
+      <c r="D13" s="27"/>
       <c r="E13" s="11"/>
-      <c r="F13" s="26"/>
+      <c r="F13" s="23"/>
       <c r="G13" s="11"/>
       <c r="H13" s="11"/>
     </row>
     <row r="14">
       <c r="A14" s="11"/>
-      <c r="B14" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
+      <c r="B14" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
       <c r="E14" s="11"/>
-      <c r="F14" s="26"/>
+      <c r="F14" s="23"/>
       <c r="G14" s="11"/>
       <c r="H14" s="11"/>
     </row>
     <row r="15">
-      <c r="A15" s="18"/>
-      <c r="B15" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" s="29"/>
+      <c r="A15" s="15"/>
+      <c r="B15" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="30"/>
       <c r="D15" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E15" s="18"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
+        <v>47</v>
+      </c>
+      <c r="E15" s="15"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="B16" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>50</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F16" s="25" t="s">
-        <v>46</v>
+        <v>51</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>52</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11"/>
-      <c r="B17" s="31" t="s">
-        <v>48</v>
+      <c r="B17" s="32" t="s">
+        <v>54</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E17" s="11"/>
-      <c r="F17" s="26"/>
+      <c r="F17" s="23"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
     </row>
     <row r="18">
       <c r="A18" s="11"/>
-      <c r="B18" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" s="27"/>
+      <c r="B18" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" s="24"/>
       <c r="D18" s="5" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="E18" s="11"/>
-      <c r="F18" s="26"/>
+      <c r="F18" s="23"/>
       <c r="G18" s="11"/>
       <c r="H18" s="11"/>
     </row>
     <row r="19">
       <c r="A19" s="11"/>
-      <c r="B19" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="D19" s="14"/>
+      <c r="B19" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>61</v>
+      </c>
       <c r="E19" s="11"/>
-      <c r="F19" s="26"/>
+      <c r="F19" s="23"/>
       <c r="G19" s="11"/>
       <c r="H19" s="11"/>
     </row>
     <row r="20">
       <c r="A20" s="11"/>
-      <c r="B20" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="C20" s="27"/>
-      <c r="D20" s="14"/>
+      <c r="B20" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" s="24"/>
+      <c r="D20" s="6" t="s">
+        <v>63</v>
+      </c>
       <c r="E20" s="11"/>
-      <c r="F20" s="26"/>
+      <c r="F20" s="23"/>
       <c r="G20" s="11"/>
       <c r="H20" s="11"/>
     </row>
     <row r="21">
       <c r="A21" s="11"/>
-      <c r="B21" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D21" s="14"/>
+      <c r="B21" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="D21" s="27"/>
       <c r="E21" s="11"/>
-      <c r="F21" s="26"/>
+      <c r="F21" s="23"/>
       <c r="G21" s="11"/>
       <c r="H21" s="11"/>
     </row>
     <row r="22">
       <c r="A22" s="11"/>
-      <c r="B22" s="32" t="s">
-        <v>39</v>
+      <c r="B22" s="16" t="s">
+        <v>45</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D22" s="14"/>
+        <v>66</v>
+      </c>
+      <c r="D22" s="27"/>
       <c r="E22" s="11"/>
-      <c r="F22" s="26"/>
+      <c r="F22" s="23"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
     </row>
     <row r="23">
-      <c r="A23" s="18"/>
-      <c r="B23" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="D23" s="14"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
+      <c r="A23" s="15"/>
+      <c r="B23" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E23" s="15"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B24" s="33" t="s">
-        <v>60</v>
-      </c>
-      <c r="C24" s="29"/>
+        <v>69</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="30"/>
       <c r="D24" s="5" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="F24" s="25" t="s">
-        <v>63</v>
+        <v>72</v>
+      </c>
+      <c r="F24" s="22" t="s">
+        <v>73</v>
       </c>
       <c r="G24" s="9" t="s">
         <v>14</v>
@@ -1483,77 +1659,79 @@
     </row>
     <row r="25">
       <c r="A25" s="11"/>
-      <c r="B25" s="34" t="s">
-        <v>64</v>
-      </c>
-      <c r="C25" s="29"/>
+      <c r="B25" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="C25" s="30"/>
       <c r="D25" s="5" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="E25" s="11"/>
-      <c r="F25" s="26"/>
+      <c r="F25" s="23"/>
       <c r="G25" s="11"/>
       <c r="H25" s="11"/>
     </row>
     <row r="26">
       <c r="A26" s="11"/>
-      <c r="B26" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="C26" s="29"/>
+      <c r="B26" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" s="30"/>
       <c r="D26" s="5" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="E26" s="11"/>
-      <c r="F26" s="26"/>
+      <c r="F26" s="23"/>
       <c r="G26" s="11"/>
       <c r="H26" s="11"/>
     </row>
     <row r="27" ht="34.5" customHeight="1">
       <c r="A27" s="11"/>
-      <c r="B27" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="C27" s="29"/>
+      <c r="B27" s="33" t="s">
+        <v>77</v>
+      </c>
+      <c r="C27" s="30"/>
       <c r="D27" s="5" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="E27" s="11"/>
-      <c r="F27" s="26"/>
+      <c r="F27" s="23"/>
       <c r="G27" s="11"/>
       <c r="H27" s="11"/>
     </row>
     <row r="28" ht="34.5" customHeight="1">
-      <c r="A28" s="18"/>
-      <c r="B28" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="C28" s="27"/>
+      <c r="A28" s="15"/>
+      <c r="B28" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="C28" s="24"/>
       <c r="D28" s="5" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="E28" s="11"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="18"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="15"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B29" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="C29" s="27"/>
-      <c r="D29" s="14"/>
+        <v>80</v>
+      </c>
+      <c r="B29" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="C29" s="24"/>
+      <c r="D29" s="6" t="s">
+        <v>82</v>
+      </c>
       <c r="E29" s="7" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="H29" s="10" t="s">
         <v>15</v>
@@ -1561,11 +1739,13 @@
     </row>
     <row r="30">
       <c r="A30" s="11"/>
-      <c r="B30" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="C30" s="27"/>
-      <c r="D30" s="14"/>
+      <c r="B30" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="C30" s="24"/>
+      <c r="D30" s="6" t="s">
+        <v>86</v>
+      </c>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="11"/>
@@ -1573,11 +1753,13 @@
     </row>
     <row r="31">
       <c r="A31" s="11"/>
-      <c r="B31" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="C31" s="27"/>
-      <c r="D31" s="14"/>
+      <c r="B31" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="C31" s="24"/>
+      <c r="D31" s="6" t="s">
+        <v>88</v>
+      </c>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="11"/>
@@ -1585,11 +1767,13 @@
     </row>
     <row r="32">
       <c r="A32" s="11"/>
-      <c r="B32" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="C32" s="27"/>
-      <c r="D32" s="14"/>
+      <c r="B32" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" s="24"/>
+      <c r="D32" s="6" t="s">
+        <v>88</v>
+      </c>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="11"/>
@@ -1597,12 +1781,12 @@
     </row>
     <row r="33" ht="19.5" customHeight="1">
       <c r="A33" s="11"/>
-      <c r="B33" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="C33" s="27"/>
+      <c r="B33" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C33" s="24"/>
       <c r="D33" s="5" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E33" s="11"/>
       <c r="F33" s="11"/>
@@ -1610,50 +1794,54 @@
       <c r="H33" s="11"/>
     </row>
     <row r="34" ht="19.5" customHeight="1">
-      <c r="A34" s="18"/>
-      <c r="B34" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="C34" s="27"/>
+      <c r="A34" s="15"/>
+      <c r="B34" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>92</v>
+      </c>
       <c r="D34" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="18"/>
+        <v>93</v>
+      </c>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="15"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B35" s="34" t="s">
-        <v>79</v>
-      </c>
-      <c r="C35" s="29"/>
+        <v>94</v>
+      </c>
+      <c r="B35" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="C35" s="30"/>
       <c r="D35" s="6" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="11"/>
-      <c r="B36" s="33" t="s">
-        <v>84</v>
-      </c>
-      <c r="C36" s="29"/>
-      <c r="D36" s="16"/>
+      <c r="B36" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="C36" s="30"/>
+      <c r="D36" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="11"/>
@@ -1661,12 +1849,12 @@
     </row>
     <row r="37">
       <c r="A37" s="11"/>
-      <c r="B37" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="C37" s="27"/>
+      <c r="B37" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C37" s="24"/>
       <c r="D37" s="5" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
@@ -1675,56 +1863,60 @@
     </row>
     <row r="38" ht="30.75" customHeight="1">
       <c r="A38" s="11"/>
-      <c r="B38" s="35" t="s">
-        <v>86</v>
-      </c>
-      <c r="C38" s="27"/>
-      <c r="D38" s="16"/>
+      <c r="B38" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="C38" s="24"/>
+      <c r="D38" s="6" t="s">
+        <v>104</v>
+      </c>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="11"/>
       <c r="H38" s="11"/>
     </row>
     <row r="39">
-      <c r="A39" s="18"/>
-      <c r="B39" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="C39" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="D39" s="16"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="18"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="18"/>
+      <c r="A39" s="15"/>
+      <c r="B39" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E39" s="15"/>
+      <c r="F39" s="15"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="15"/>
     </row>
     <row r="40">
-      <c r="A40" s="36"/>
-      <c r="B40" s="37"/>
-      <c r="C40" s="38"/>
-      <c r="D40" s="39"/>
-      <c r="E40" s="40"/>
-      <c r="F40" s="41"/>
-      <c r="G40" s="42"/>
+      <c r="A40" s="34"/>
+      <c r="B40" s="35"/>
+      <c r="C40" s="36"/>
+      <c r="D40" s="37"/>
+      <c r="E40" s="38"/>
+      <c r="F40" s="39"/>
+      <c r="G40" s="40"/>
     </row>
     <row r="41">
-      <c r="A41" s="36"/>
-      <c r="B41" s="37"/>
-      <c r="C41" s="38"/>
-      <c r="D41" s="39"/>
-      <c r="E41" s="40"/>
-      <c r="F41" s="41"/>
-      <c r="G41" s="42"/>
+      <c r="A41" s="34"/>
+      <c r="B41" s="35"/>
+      <c r="C41" s="36"/>
+      <c r="D41" s="37"/>
+      <c r="E41" s="38"/>
+      <c r="F41" s="39"/>
+      <c r="G41" s="40"/>
     </row>
     <row r="42">
-      <c r="A42" s="36"/>
-      <c r="B42" s="37"/>
-      <c r="C42" s="38"/>
-      <c r="D42" s="39"/>
-      <c r="E42" s="40"/>
-      <c r="F42" s="41"/>
-      <c r="G42" s="42"/>
+      <c r="A42" s="34"/>
+      <c r="B42" s="35"/>
+      <c r="C42" s="36"/>
+      <c r="D42" s="37"/>
+      <c r="E42" s="38"/>
+      <c r="F42" s="39"/>
+      <c r="G42" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -1764,33 +1956,50 @@
     <hyperlink r:id="rId2" ref="D2"/>
     <hyperlink r:id="rId3" ref="D3"/>
     <hyperlink r:id="rId4" ref="C4"/>
-    <hyperlink r:id="rId5" ref="C6"/>
-    <hyperlink r:id="rId6" ref="D6"/>
-    <hyperlink r:id="rId7" ref="D7"/>
-    <hyperlink r:id="rId8" ref="C9"/>
-    <hyperlink r:id="rId9" ref="C10"/>
-    <hyperlink r:id="rId10" ref="D15"/>
-    <hyperlink r:id="rId11" ref="C16"/>
-    <hyperlink r:id="rId12" location="slide=id.p2" ref="D16"/>
-    <hyperlink r:id="rId13" ref="C17"/>
-    <hyperlink r:id="rId14" ref="D17"/>
-    <hyperlink r:id="rId15" ref="D18"/>
-    <hyperlink r:id="rId16" ref="C19"/>
-    <hyperlink r:id="rId17" ref="C21"/>
-    <hyperlink r:id="rId18" ref="C22"/>
-    <hyperlink r:id="rId19" ref="C23"/>
-    <hyperlink r:id="rId20" ref="D24"/>
-    <hyperlink r:id="rId21" ref="D25"/>
-    <hyperlink r:id="rId22" ref="D26"/>
-    <hyperlink r:id="rId23" ref="D27"/>
-    <hyperlink r:id="rId24" ref="D28"/>
-    <hyperlink r:id="rId25" ref="D33"/>
-    <hyperlink r:id="rId26" ref="D34"/>
-    <hyperlink r:id="rId27" ref="D35"/>
-    <hyperlink r:id="rId28" ref="D37"/>
-    <hyperlink r:id="rId29" ref="C39"/>
+    <hyperlink r:id="rId5" ref="D4"/>
+    <hyperlink r:id="rId6" ref="D5"/>
+    <hyperlink r:id="rId7" ref="C6"/>
+    <hyperlink r:id="rId8" ref="D6"/>
+    <hyperlink r:id="rId9" ref="D7"/>
+    <hyperlink r:id="rId10" ref="D8"/>
+    <hyperlink r:id="rId11" ref="C9"/>
+    <hyperlink r:id="rId12" ref="D9"/>
+    <hyperlink r:id="rId13" ref="C10"/>
+    <hyperlink r:id="rId14" ref="D10"/>
+    <hyperlink r:id="rId15" ref="D11"/>
+    <hyperlink r:id="rId16" ref="D15"/>
+    <hyperlink r:id="rId17" ref="C16"/>
+    <hyperlink r:id="rId18" location="slide=id.p2" ref="D16"/>
+    <hyperlink r:id="rId19" ref="C17"/>
+    <hyperlink r:id="rId20" ref="D17"/>
+    <hyperlink r:id="rId21" ref="D18"/>
+    <hyperlink r:id="rId22" ref="C19"/>
+    <hyperlink r:id="rId23" ref="D19"/>
+    <hyperlink r:id="rId24" ref="D20"/>
+    <hyperlink r:id="rId25" ref="C21"/>
+    <hyperlink r:id="rId26" ref="C22"/>
+    <hyperlink r:id="rId27" ref="C23"/>
+    <hyperlink r:id="rId28" location="slide=id.p1" ref="D23"/>
+    <hyperlink r:id="rId29" ref="D24"/>
+    <hyperlink r:id="rId30" ref="D25"/>
+    <hyperlink r:id="rId31" ref="D26"/>
+    <hyperlink r:id="rId32" ref="D27"/>
+    <hyperlink r:id="rId33" ref="D28"/>
+    <hyperlink r:id="rId34" ref="D29"/>
+    <hyperlink r:id="rId35" ref="D30"/>
+    <hyperlink r:id="rId36" ref="D31"/>
+    <hyperlink r:id="rId37" ref="D32"/>
+    <hyperlink r:id="rId38" ref="D33"/>
+    <hyperlink r:id="rId39" ref="C34"/>
+    <hyperlink r:id="rId40" ref="D34"/>
+    <hyperlink r:id="rId41" ref="D35"/>
+    <hyperlink r:id="rId42" ref="D36"/>
+    <hyperlink r:id="rId43" ref="D37"/>
+    <hyperlink r:id="rId44" ref="D38"/>
+    <hyperlink r:id="rId45" ref="C39"/>
+    <hyperlink r:id="rId46" ref="D39"/>
   </hyperlinks>
-  <drawing r:id="rId30"/>
+  <drawing r:id="rId47"/>
 </worksheet>
 </file>
 
@@ -1837,358 +2046,396 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="B2" s="24" t="s">
-        <v>28</v>
+      <c r="A2" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>31</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D2" s="14"/>
+        <v>107</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>108</v>
+      </c>
       <c r="E2" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="F2" s="25" t="s">
-        <v>91</v>
+        <v>109</v>
+      </c>
+      <c r="F2" s="22" t="s">
+        <v>110</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11"/>
-      <c r="B3" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="14"/>
+      <c r="B3" s="41" t="s">
+        <v>112</v>
+      </c>
+      <c r="C3" s="30"/>
+      <c r="D3" s="25" t="s">
+        <v>113</v>
+      </c>
       <c r="E3" s="11"/>
-      <c r="F3" s="26"/>
+      <c r="F3" s="23"/>
       <c r="G3" s="11"/>
       <c r="H3" s="11"/>
     </row>
     <row r="4">
       <c r="A4" s="11"/>
-      <c r="B4" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="C4" s="27"/>
-      <c r="D4" s="14"/>
+      <c r="B4" s="41" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4" s="24"/>
+      <c r="D4" s="25" t="s">
+        <v>115</v>
+      </c>
       <c r="E4" s="11"/>
-      <c r="F4" s="26"/>
+      <c r="F4" s="23"/>
       <c r="G4" s="11"/>
       <c r="H4" s="11"/>
     </row>
     <row r="5">
       <c r="A5" s="11"/>
-      <c r="B5" s="28" t="s">
-        <v>95</v>
+      <c r="B5" s="41" t="s">
+        <v>116</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D5" s="14"/>
+        <v>66</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>117</v>
+      </c>
       <c r="E5" s="11"/>
-      <c r="F5" s="26"/>
+      <c r="F5" s="23"/>
       <c r="G5" s="11"/>
       <c r="H5" s="11"/>
     </row>
     <row r="6">
       <c r="A6" s="11"/>
-      <c r="B6" s="28" t="s">
-        <v>40</v>
+      <c r="B6" s="41" t="s">
+        <v>46</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="14"/>
+        <v>47</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>118</v>
+      </c>
       <c r="E6" s="11"/>
-      <c r="F6" s="26"/>
+      <c r="F6" s="23"/>
       <c r="G6" s="11"/>
       <c r="H6" s="11"/>
     </row>
     <row r="7" ht="30.0" customHeight="1">
-      <c r="A7" s="18"/>
-      <c r="B7" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="27"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
+      <c r="A7" s="15"/>
+      <c r="B7" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="24"/>
+      <c r="D7" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="E7" s="15"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="D8" s="14"/>
+        <v>120</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>122</v>
+      </c>
       <c r="E8" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="F8" s="25" t="s">
-        <v>99</v>
+        <v>123</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>124</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11"/>
-      <c r="B9" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" s="14"/>
+      <c r="B9" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="11"/>
+      <c r="D9" s="25" t="s">
+        <v>125</v>
+      </c>
       <c r="E9" s="11"/>
-      <c r="F9" s="26"/>
+      <c r="F9" s="23"/>
       <c r="G9" s="11"/>
       <c r="H9" s="11"/>
     </row>
     <row r="10">
       <c r="A10" s="11"/>
-      <c r="B10" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10" s="29"/>
+      <c r="B10" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="11"/>
       <c r="D10" s="5" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="E10" s="11"/>
-      <c r="F10" s="26"/>
+      <c r="F10" s="23"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
     </row>
     <row r="11">
       <c r="A11" s="11"/>
-      <c r="B11" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="D11" s="14"/>
+      <c r="B11" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="11"/>
+      <c r="D11" s="25" t="s">
+        <v>127</v>
+      </c>
       <c r="E11" s="11"/>
-      <c r="F11" s="26"/>
+      <c r="F11" s="23"/>
       <c r="G11" s="11"/>
       <c r="H11" s="11"/>
     </row>
     <row r="12">
       <c r="A12" s="11"/>
-      <c r="B12" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="C12" s="27"/>
-      <c r="D12" s="14"/>
+      <c r="B12" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="11"/>
+      <c r="D12" s="25" t="s">
+        <v>128</v>
+      </c>
       <c r="E12" s="11"/>
-      <c r="F12" s="26"/>
+      <c r="F12" s="23"/>
       <c r="G12" s="11"/>
       <c r="H12" s="11"/>
     </row>
     <row r="13">
       <c r="A13" s="11"/>
-      <c r="B13" s="28" t="s">
-        <v>102</v>
-      </c>
-      <c r="C13" s="27"/>
-      <c r="D13" s="14"/>
+      <c r="B13" s="41" t="s">
+        <v>129</v>
+      </c>
+      <c r="C13" s="11"/>
+      <c r="D13" s="43" t="s">
+        <v>130</v>
+      </c>
       <c r="E13" s="11"/>
-      <c r="F13" s="26"/>
+      <c r="F13" s="23"/>
       <c r="G13" s="11"/>
       <c r="H13" s="11"/>
     </row>
     <row r="14">
       <c r="A14" s="11"/>
-      <c r="B14" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="27"/>
-      <c r="D14" s="14"/>
+      <c r="B14" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="11"/>
+      <c r="D14" s="25" t="s">
+        <v>131</v>
+      </c>
       <c r="E14" s="11"/>
-      <c r="F14" s="26"/>
+      <c r="F14" s="23"/>
       <c r="G14" s="11"/>
       <c r="H14" s="11"/>
     </row>
     <row r="15">
       <c r="A15" s="11"/>
-      <c r="B15" s="28" t="s">
-        <v>103</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D15" s="14"/>
+      <c r="B15" s="41" t="s">
+        <v>132</v>
+      </c>
+      <c r="C15" s="11"/>
+      <c r="D15" s="25" t="s">
+        <v>133</v>
+      </c>
       <c r="E15" s="11"/>
-      <c r="F15" s="26"/>
+      <c r="F15" s="23"/>
       <c r="G15" s="11"/>
       <c r="H15" s="11"/>
     </row>
     <row r="16">
-      <c r="A16" s="18"/>
-      <c r="B16" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="C16" s="29"/>
+      <c r="A16" s="15"/>
+      <c r="B16" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="15"/>
       <c r="D16" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E16" s="18"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18"/>
+        <v>47</v>
+      </c>
+      <c r="E16" s="15"/>
+      <c r="F16" s="31"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B17" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="C17" s="27"/>
+        <v>134</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" s="24"/>
       <c r="D17" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="E17" s="7"/>
-      <c r="F17" s="25"/>
+        <v>126</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>136</v>
+      </c>
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
     </row>
     <row r="18">
       <c r="A18" s="11"/>
-      <c r="B18" s="28" t="s">
-        <v>105</v>
-      </c>
-      <c r="C18" s="27"/>
-      <c r="D18" s="14"/>
+      <c r="B18" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="C18" s="24"/>
+      <c r="D18" s="25" t="s">
+        <v>138</v>
+      </c>
       <c r="E18" s="11"/>
-      <c r="F18" s="26"/>
+      <c r="F18" s="23"/>
       <c r="G18" s="11"/>
       <c r="H18" s="11"/>
     </row>
     <row r="19">
       <c r="A19" s="11"/>
-      <c r="B19" s="28" t="s">
-        <v>106</v>
-      </c>
-      <c r="C19" s="27"/>
-      <c r="D19" s="14"/>
+      <c r="B19" s="41" t="s">
+        <v>139</v>
+      </c>
+      <c r="C19" s="24"/>
+      <c r="D19" s="25" t="s">
+        <v>140</v>
+      </c>
       <c r="E19" s="11"/>
-      <c r="F19" s="26"/>
+      <c r="F19" s="23"/>
       <c r="G19" s="11"/>
       <c r="H19" s="11"/>
     </row>
     <row r="20">
       <c r="A20" s="11"/>
-      <c r="B20" s="28" t="s">
-        <v>107</v>
+      <c r="B20" s="41" t="s">
+        <v>141</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D20" s="14"/>
+        <v>66</v>
+      </c>
+      <c r="D20" s="25" t="s">
+        <v>142</v>
+      </c>
       <c r="E20" s="11"/>
-      <c r="F20" s="26"/>
+      <c r="F20" s="23"/>
       <c r="G20" s="11"/>
       <c r="H20" s="11"/>
     </row>
     <row r="21">
       <c r="A21" s="11"/>
-      <c r="B21" s="28" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" s="27"/>
-      <c r="D21" s="14"/>
+      <c r="B21" s="41" t="s">
+        <v>100</v>
+      </c>
+      <c r="C21" s="24"/>
+      <c r="D21" s="25" t="s">
+        <v>143</v>
+      </c>
       <c r="E21" s="11"/>
-      <c r="F21" s="26"/>
+      <c r="F21" s="23"/>
       <c r="G21" s="11"/>
       <c r="H21" s="11"/>
     </row>
     <row r="22">
       <c r="A22" s="11"/>
-      <c r="B22" s="28" t="s">
-        <v>108</v>
-      </c>
-      <c r="C22" s="27"/>
+      <c r="B22" s="41" t="s">
+        <v>144</v>
+      </c>
+      <c r="C22" s="24"/>
       <c r="D22" s="5" t="s">
-        <v>109</v>
+        <v>145</v>
       </c>
       <c r="E22" s="11"/>
-      <c r="F22" s="26"/>
+      <c r="F22" s="23"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
     </row>
     <row r="23" ht="34.5" customHeight="1">
       <c r="A23" s="11"/>
-      <c r="B23" s="43" t="s">
-        <v>110</v>
-      </c>
-      <c r="C23" s="27"/>
-      <c r="D23" s="14"/>
+      <c r="B23" s="44" t="s">
+        <v>146</v>
+      </c>
+      <c r="C23" s="24"/>
+      <c r="D23" s="25" t="s">
+        <v>147</v>
+      </c>
       <c r="E23" s="11"/>
-      <c r="F23" s="26"/>
+      <c r="F23" s="23"/>
       <c r="G23" s="11"/>
       <c r="H23" s="11"/>
     </row>
     <row r="24" ht="34.5" customHeight="1">
-      <c r="A24" s="18"/>
-      <c r="B24" s="28" t="s">
-        <v>111</v>
-      </c>
-      <c r="C24" s="27"/>
+      <c r="A24" s="15"/>
+      <c r="B24" s="41" t="s">
+        <v>148</v>
+      </c>
+      <c r="C24" s="24"/>
       <c r="D24" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E24" s="11"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
+        <v>47</v>
+      </c>
+      <c r="E24" s="15"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="B25" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="C25" s="27"/>
-      <c r="D25" s="14"/>
+        <v>149</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" s="24"/>
+      <c r="D25" s="6" t="s">
+        <v>150</v>
+      </c>
       <c r="E25" s="7" t="s">
-        <v>113</v>
+        <v>151</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>114</v>
+        <v>152</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>115</v>
+        <v>153</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11"/>
-      <c r="B26" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="C26" s="27"/>
-      <c r="D26" s="14"/>
+      <c r="B26" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" s="24"/>
+      <c r="D26" s="6" t="s">
+        <v>154</v>
+      </c>
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
       <c r="G26" s="11"/>
@@ -2196,11 +2443,13 @@
     </row>
     <row r="27">
       <c r="A27" s="11"/>
-      <c r="B27" s="28" t="s">
-        <v>116</v>
-      </c>
-      <c r="C27" s="27"/>
-      <c r="D27" s="14"/>
+      <c r="B27" s="41" t="s">
+        <v>155</v>
+      </c>
+      <c r="C27" s="24"/>
+      <c r="D27" s="25" t="s">
+        <v>156</v>
+      </c>
       <c r="E27" s="11"/>
       <c r="F27" s="11"/>
       <c r="G27" s="11"/>
@@ -2208,11 +2457,13 @@
     </row>
     <row r="28">
       <c r="A28" s="11"/>
-      <c r="B28" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="C28" s="27"/>
-      <c r="D28" s="14"/>
+      <c r="B28" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="C28" s="24"/>
+      <c r="D28" s="25" t="s">
+        <v>157</v>
+      </c>
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
       <c r="G28" s="11"/>
@@ -2220,12 +2471,12 @@
     </row>
     <row r="29" ht="19.5" customHeight="1">
       <c r="A29" s="11"/>
-      <c r="B29" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="C29" s="27"/>
+      <c r="B29" s="41" t="s">
+        <v>90</v>
+      </c>
+      <c r="C29" s="24"/>
       <c r="D29" s="5" t="s">
-        <v>41</v>
+        <v>158</v>
       </c>
       <c r="E29" s="11"/>
       <c r="F29" s="11"/>
@@ -2233,48 +2484,52 @@
       <c r="H29" s="11"/>
     </row>
     <row r="30" ht="19.5" customHeight="1">
-      <c r="A30" s="18"/>
-      <c r="B30" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="C30" s="27"/>
+      <c r="A30" s="15"/>
+      <c r="B30" s="41" t="s">
+        <v>91</v>
+      </c>
+      <c r="C30" s="24"/>
       <c r="D30" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18"/>
+        <v>159</v>
+      </c>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="15"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B31" s="28" t="s">
-        <v>118</v>
-      </c>
-      <c r="C31" s="27"/>
-      <c r="D31" s="14"/>
+        <v>160</v>
+      </c>
+      <c r="B31" s="41" t="s">
+        <v>161</v>
+      </c>
+      <c r="C31" s="24"/>
+      <c r="D31" s="25" t="s">
+        <v>162</v>
+      </c>
       <c r="E31" s="7" t="s">
-        <v>119</v>
+        <v>163</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>115</v>
+        <v>153</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="11"/>
-      <c r="B32" s="28" t="s">
-        <v>121</v>
-      </c>
-      <c r="C32" s="27"/>
-      <c r="D32" s="14"/>
+      <c r="B32" s="41" t="s">
+        <v>165</v>
+      </c>
+      <c r="C32" s="24"/>
+      <c r="D32" s="25" t="s">
+        <v>166</v>
+      </c>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="11"/>
@@ -2282,13 +2537,15 @@
     </row>
     <row r="33">
       <c r="A33" s="11"/>
-      <c r="B33" s="28" t="s">
-        <v>95</v>
+      <c r="B33" s="41" t="s">
+        <v>116</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D33" s="14"/>
+        <v>66</v>
+      </c>
+      <c r="D33" s="25" t="s">
+        <v>167</v>
+      </c>
       <c r="E33" s="11"/>
       <c r="F33" s="11"/>
       <c r="G33" s="11"/>
@@ -2296,12 +2553,12 @@
     </row>
     <row r="34">
       <c r="A34" s="11"/>
-      <c r="B34" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="C34" s="27"/>
+      <c r="B34" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="C34" s="24"/>
       <c r="D34" s="5" t="s">
-        <v>41</v>
+        <v>168</v>
       </c>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
@@ -2309,93 +2566,119 @@
       <c r="H34" s="11"/>
     </row>
     <row r="35" ht="34.5" customHeight="1">
-      <c r="A35" s="18"/>
-      <c r="B35" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="C35" s="27"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="18"/>
-      <c r="H35" s="18"/>
+      <c r="A35" s="15"/>
+      <c r="B35" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" s="24"/>
+      <c r="D35" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="15"/>
     </row>
     <row r="36">
-      <c r="A36" s="36"/>
-      <c r="B36" s="37"/>
-      <c r="E36" s="40"/>
-      <c r="F36" s="41"/>
-      <c r="G36" s="42"/>
+      <c r="A36" s="34"/>
+      <c r="B36" s="35"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="39"/>
+      <c r="G36" s="40"/>
     </row>
     <row r="37">
-      <c r="A37" s="36"/>
-      <c r="B37" s="37"/>
-      <c r="E37" s="40"/>
-      <c r="F37" s="41"/>
-      <c r="G37" s="42"/>
+      <c r="A37" s="34"/>
+      <c r="B37" s="35"/>
+      <c r="E37" s="38"/>
+      <c r="F37" s="39"/>
+      <c r="G37" s="40"/>
     </row>
     <row r="38">
-      <c r="A38" s="36"/>
-      <c r="B38" s="37"/>
-      <c r="E38" s="40"/>
-      <c r="F38" s="41"/>
-      <c r="G38" s="42"/>
+      <c r="A38" s="34"/>
+      <c r="B38" s="35"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="39"/>
+      <c r="G38" s="40"/>
     </row>
     <row r="39">
-      <c r="A39" s="36"/>
-      <c r="B39" s="37"/>
-      <c r="E39" s="40"/>
-      <c r="F39" s="41"/>
-      <c r="G39" s="42"/>
+      <c r="A39" s="34"/>
+      <c r="B39" s="35"/>
+      <c r="E39" s="38"/>
+      <c r="F39" s="39"/>
+      <c r="G39" s="40"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="26">
+    <mergeCell ref="E8:E16"/>
+    <mergeCell ref="F8:F16"/>
+    <mergeCell ref="G8:G16"/>
+    <mergeCell ref="H8:H16"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="E17:E24"/>
+    <mergeCell ref="E25:E30"/>
+    <mergeCell ref="E31:E35"/>
+    <mergeCell ref="F17:F24"/>
+    <mergeCell ref="G17:G24"/>
+    <mergeCell ref="F25:F30"/>
+    <mergeCell ref="G25:G30"/>
+    <mergeCell ref="H25:H30"/>
+    <mergeCell ref="F31:F35"/>
+    <mergeCell ref="G31:G35"/>
+    <mergeCell ref="H31:H35"/>
+    <mergeCell ref="A17:A24"/>
     <mergeCell ref="A25:A30"/>
+    <mergeCell ref="A31:A35"/>
     <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A17:A24"/>
-    <mergeCell ref="A8:A16"/>
-    <mergeCell ref="A31:A35"/>
-    <mergeCell ref="E2:E7"/>
     <mergeCell ref="F2:F7"/>
     <mergeCell ref="G2:G7"/>
     <mergeCell ref="H2:H7"/>
-    <mergeCell ref="E8:E16"/>
-    <mergeCell ref="H8:H16"/>
-    <mergeCell ref="F8:F16"/>
-    <mergeCell ref="G8:G16"/>
-    <mergeCell ref="F25:F30"/>
-    <mergeCell ref="G25:G30"/>
-    <mergeCell ref="F31:F35"/>
-    <mergeCell ref="G31:G35"/>
-    <mergeCell ref="H31:H35"/>
-    <mergeCell ref="E25:E30"/>
-    <mergeCell ref="E17:E24"/>
-    <mergeCell ref="F17:F24"/>
-    <mergeCell ref="G17:G24"/>
-    <mergeCell ref="E31:E35"/>
-    <mergeCell ref="H25:H30"/>
+    <mergeCell ref="A8:A16"/>
+    <mergeCell ref="C8:C16"/>
     <mergeCell ref="H17:H24"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="C2"/>
-    <hyperlink r:id="rId2" ref="C5"/>
-    <hyperlink r:id="rId3" ref="C6"/>
-    <hyperlink r:id="rId4" ref="C8"/>
-    <hyperlink r:id="rId5" ref="C9"/>
-    <hyperlink r:id="rId6" ref="D10"/>
-    <hyperlink r:id="rId7" ref="C11"/>
-    <hyperlink r:id="rId8" ref="C15"/>
-    <hyperlink r:id="rId9" ref="D16"/>
-    <hyperlink r:id="rId10" ref="D17"/>
-    <hyperlink r:id="rId11" ref="C20"/>
-    <hyperlink r:id="rId12" ref="D22"/>
-    <hyperlink r:id="rId13" ref="D24"/>
-    <hyperlink r:id="rId14" ref="D29"/>
-    <hyperlink r:id="rId15" ref="D30"/>
-    <hyperlink r:id="rId16" ref="C33"/>
-    <hyperlink r:id="rId17" ref="D34"/>
+    <hyperlink r:id="rId2" ref="D2"/>
+    <hyperlink r:id="rId3" ref="D3"/>
+    <hyperlink r:id="rId4" ref="D4"/>
+    <hyperlink r:id="rId5" ref="C5"/>
+    <hyperlink r:id="rId6" ref="D5"/>
+    <hyperlink r:id="rId7" ref="C6"/>
+    <hyperlink r:id="rId8" ref="D6"/>
+    <hyperlink r:id="rId9" ref="D7"/>
+    <hyperlink r:id="rId10" ref="C8"/>
+    <hyperlink r:id="rId11" ref="D8"/>
+    <hyperlink r:id="rId12" ref="D9"/>
+    <hyperlink r:id="rId13" ref="D10"/>
+    <hyperlink r:id="rId14" ref="D11"/>
+    <hyperlink r:id="rId15" ref="D12"/>
+    <hyperlink r:id="rId16" ref="D13"/>
+    <hyperlink r:id="rId17" ref="D14"/>
+    <hyperlink r:id="rId18" ref="D15"/>
+    <hyperlink r:id="rId19" ref="D16"/>
+    <hyperlink r:id="rId20" ref="D17"/>
+    <hyperlink r:id="rId21" ref="D18"/>
+    <hyperlink r:id="rId22" ref="D19"/>
+    <hyperlink r:id="rId23" ref="C20"/>
+    <hyperlink r:id="rId24" ref="D20"/>
+    <hyperlink r:id="rId25" ref="D21"/>
+    <hyperlink r:id="rId26" ref="D22"/>
+    <hyperlink r:id="rId27" ref="D23"/>
+    <hyperlink r:id="rId28" ref="D24"/>
+    <hyperlink r:id="rId29" ref="D25"/>
+    <hyperlink r:id="rId30" ref="D26"/>
+    <hyperlink r:id="rId31" ref="D27"/>
+    <hyperlink r:id="rId32" ref="D28"/>
+    <hyperlink r:id="rId33" ref="D29"/>
+    <hyperlink r:id="rId34" ref="D30"/>
+    <hyperlink r:id="rId35" ref="D31"/>
+    <hyperlink r:id="rId36" ref="D32"/>
+    <hyperlink r:id="rId37" ref="C33"/>
+    <hyperlink r:id="rId38" ref="D33"/>
+    <hyperlink r:id="rId39" ref="D34"/>
+    <hyperlink r:id="rId40" ref="D35"/>
   </hyperlinks>
-  <drawing r:id="rId18"/>
+  <drawing r:id="rId41"/>
 </worksheet>
 </file>
 
@@ -2443,37 +2726,37 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="B2" s="28" t="s">
-        <v>123</v>
+        <v>170</v>
+      </c>
+      <c r="B2" s="41" t="s">
+        <v>171</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="D2" s="44" t="s">
-        <v>125</v>
+        <v>172</v>
+      </c>
+      <c r="D2" s="45" t="s">
+        <v>173</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>126</v>
+        <v>174</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>127</v>
+        <v>175</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>128</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11"/>
-      <c r="B3" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
+      <c r="B3" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="11"/>
@@ -2481,11 +2764,11 @@
     </row>
     <row r="4">
       <c r="A4" s="11"/>
-      <c r="B4" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="D4" s="44" t="s">
-        <v>130</v>
+      <c r="B4" s="41" t="s">
+        <v>177</v>
+      </c>
+      <c r="D4" s="45" t="s">
+        <v>178</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
@@ -2494,12 +2777,12 @@
     </row>
     <row r="5">
       <c r="A5" s="11"/>
-      <c r="B5" s="28" t="s">
-        <v>131</v>
-      </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="44" t="s">
-        <v>132</v>
+      <c r="B5" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="C5" s="24"/>
+      <c r="D5" s="45" t="s">
+        <v>180</v>
       </c>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
@@ -2508,14 +2791,14 @@
     </row>
     <row r="6" ht="17.25" customHeight="1">
       <c r="A6" s="11"/>
-      <c r="B6" s="28" t="s">
-        <v>106</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="D6" s="44" t="s">
-        <v>134</v>
+      <c r="B6" s="41" t="s">
+        <v>181</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="D6" s="45" t="s">
+        <v>183</v>
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
@@ -2524,11 +2807,11 @@
     </row>
     <row r="7">
       <c r="A7" s="11"/>
-      <c r="B7" s="28" t="s">
-        <v>107</v>
-      </c>
-      <c r="D7" s="45" t="s">
-        <v>57</v>
+      <c r="B7" s="41" t="s">
+        <v>141</v>
+      </c>
+      <c r="D7" s="46" t="s">
+        <v>66</v>
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
@@ -2537,11 +2820,11 @@
     </row>
     <row r="8">
       <c r="A8" s="11"/>
-      <c r="B8" s="28" t="s">
-        <v>135</v>
-      </c>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
+      <c r="B8" s="41" t="s">
+        <v>184</v>
+      </c>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
@@ -2549,11 +2832,11 @@
     </row>
     <row r="9">
       <c r="A9" s="11"/>
-      <c r="B9" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" s="44" t="s">
-        <v>136</v>
+      <c r="B9" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="45" t="s">
+        <v>185</v>
       </c>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
@@ -2562,59 +2845,59 @@
     </row>
     <row r="10" ht="19.5" customHeight="1">
       <c r="A10" s="11"/>
-      <c r="B10" s="43" t="s">
-        <v>137</v>
-      </c>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
+      <c r="B10" s="44" t="s">
+        <v>186</v>
+      </c>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
     </row>
     <row r="11" ht="21.75" customHeight="1">
-      <c r="A11" s="18"/>
-      <c r="B11" s="28" t="s">
-        <v>111</v>
-      </c>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
+      <c r="A11" s="15"/>
+      <c r="B11" s="41" t="s">
+        <v>148</v>
+      </c>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="B12" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="C12" s="27"/>
-      <c r="D12" s="44" t="s">
-        <v>125</v>
+        <v>187</v>
+      </c>
+      <c r="B12" s="41" t="s">
+        <v>188</v>
+      </c>
+      <c r="C12" s="24"/>
+      <c r="D12" s="45" t="s">
+        <v>173</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>139</v>
+        <v>189</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>128</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11"/>
-      <c r="B13" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27"/>
+      <c r="B13" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="11"/>
@@ -2622,11 +2905,11 @@
     </row>
     <row r="14">
       <c r="A14" s="11"/>
-      <c r="B14" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="D14" s="44" t="s">
-        <v>130</v>
+      <c r="B14" s="41" t="s">
+        <v>177</v>
+      </c>
+      <c r="D14" s="45" t="s">
+        <v>178</v>
       </c>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
@@ -2635,12 +2918,12 @@
     </row>
     <row r="15">
       <c r="A15" s="11"/>
-      <c r="B15" s="28" t="s">
-        <v>131</v>
-      </c>
-      <c r="C15" s="27"/>
-      <c r="D15" s="44" t="s">
-        <v>132</v>
+      <c r="B15" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="C15" s="24"/>
+      <c r="D15" s="45" t="s">
+        <v>180</v>
       </c>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
@@ -2649,12 +2932,12 @@
     </row>
     <row r="16">
       <c r="A16" s="11"/>
-      <c r="B16" s="28" t="s">
-        <v>106</v>
-      </c>
-      <c r="C16" s="27"/>
-      <c r="D16" s="44" t="s">
-        <v>134</v>
+      <c r="B16" s="41" t="s">
+        <v>181</v>
+      </c>
+      <c r="C16" s="24"/>
+      <c r="D16" s="45" t="s">
+        <v>183</v>
       </c>
       <c r="E16" s="11"/>
       <c r="F16" s="11"/>
@@ -2663,14 +2946,14 @@
     </row>
     <row r="17">
       <c r="A17" s="11"/>
-      <c r="B17" s="28" t="s">
-        <v>107</v>
-      </c>
-      <c r="C17" s="45" t="s">
-        <v>57</v>
-      </c>
-      <c r="D17" s="45" t="s">
-        <v>57</v>
+      <c r="B17" s="41" t="s">
+        <v>141</v>
+      </c>
+      <c r="C17" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" s="46" t="s">
+        <v>66</v>
       </c>
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
@@ -2679,11 +2962,11 @@
     </row>
     <row r="18">
       <c r="A18" s="11"/>
-      <c r="B18" s="28" t="s">
-        <v>141</v>
-      </c>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
+      <c r="B18" s="41" t="s">
+        <v>191</v>
+      </c>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
@@ -2691,11 +2974,11 @@
     </row>
     <row r="19">
       <c r="A19" s="11"/>
-      <c r="B19" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="44" t="s">
-        <v>136</v>
+      <c r="B19" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="45" t="s">
+        <v>185</v>
       </c>
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
@@ -2704,27 +2987,27 @@
     </row>
     <row r="20">
       <c r="A20" s="11"/>
-      <c r="B20" s="43" t="s">
-        <v>142</v>
-      </c>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
+      <c r="B20" s="44" t="s">
+        <v>192</v>
+      </c>
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
       <c r="E20" s="11"/>
       <c r="F20" s="11"/>
       <c r="G20" s="11"/>
       <c r="H20" s="11"/>
     </row>
     <row r="21">
-      <c r="A21" s="18"/>
-      <c r="B21" s="28" t="s">
-        <v>143</v>
-      </c>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="18"/>
+      <c r="A21" s="15"/>
+      <c r="B21" s="41" t="s">
+        <v>193</v>
+      </c>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="10">
